--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_94_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_94_EL.xlsx
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M2" t="n">
         <v>8</v>
@@ -745,17 +745,17 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M3" t="n">
         <v>14</v>
@@ -904,17 +904,17 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X18" t="n">
         <v>4</v>
@@ -1929,10 +1929,10 @@
         <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X20" t="n">
         <v>5</v>
@@ -2119,7 +2119,7 @@
         <v>14</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
@@ -2517,10 +2517,10 @@
         <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X23" t="n">
         <v>1</v>
@@ -2707,7 +2707,7 @@
         <v>14</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
@@ -2903,16 +2903,16 @@
         <v>20</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X25" t="n">
         <v>3</v>
@@ -3099,16 +3099,16 @@
         <v>17</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U26" t="n">
         <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X26" t="n">
         <v>2</v>
@@ -3301,10 +3301,10 @@
         <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X27" t="n">
         <v>1</v>
@@ -3827,16 +3827,16 @@
         <v>111</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="X30" t="n">
         <v>24</v>
@@ -4295,13 +4295,13 @@
         <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X35" t="n">
         <v>12</v>
@@ -4690,10 +4690,10 @@
         <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X37" t="n">
         <v>6</v>
@@ -5082,10 +5082,10 @@
         <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X39" t="n">
         <v>5</v>
@@ -5272,16 +5272,16 @@
         <v>22</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X40" t="n">
         <v>11</v>
@@ -6454,10 +6454,10 @@
         <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X46" t="n">
         <v>3</v>
@@ -6784,16 +6784,16 @@
         <v>97</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="X48" t="n">
         <v>40</v>

--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_94_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_94_EL.xlsx
@@ -674,10 +674,10 @@
         <v>8</v>
       </c>
       <c r="N2" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="O2" t="n">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="P2" t="n">
         <v>2</v>
@@ -705,7 +705,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>70.59</t>
+          <t>52.38</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -833,10 +833,10 @@
         <v>14</v>
       </c>
       <c r="N3" t="n">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="O3" t="n">
-        <v>55</v>
+        <v>26</v>
       </c>
       <c r="P3" t="n">
         <v>1</v>
@@ -864,7 +864,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>72.73</t>
+          <t>42.31</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -1543,14 +1543,14 @@
         <v>3</v>
       </c>
       <c r="X18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="AA18" t="n">
@@ -1739,14 +1739,14 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA19" t="n">
@@ -1935,14 +1935,14 @@
         <v>2</v>
       </c>
       <c r="X20" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Y20" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="AA20" t="n">
@@ -2523,14 +2523,14 @@
         <v>1</v>
       </c>
       <c r="X23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA23" t="n">
@@ -2719,14 +2719,14 @@
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA24" t="n">
@@ -2915,14 +2915,14 @@
         <v>1</v>
       </c>
       <c r="X25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA25" t="n">
@@ -3111,14 +3111,14 @@
         <v>2</v>
       </c>
       <c r="X26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA26" t="n">
@@ -3307,14 +3307,14 @@
         <v>1</v>
       </c>
       <c r="X27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA27" t="n">
@@ -3839,14 +3839,14 @@
         <v>10</v>
       </c>
       <c r="X30" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="Y30" t="n">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>70.6%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="AA30" t="n">
@@ -4304,14 +4304,14 @@
         <v>2</v>
       </c>
       <c r="X35" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="Y35" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AA35" t="n">
@@ -4696,14 +4696,14 @@
         <v>2</v>
       </c>
       <c r="X37" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA37" t="n">
@@ -5088,14 +5088,14 @@
         <v>1</v>
       </c>
       <c r="X39" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y39" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="AA39" t="n">
@@ -5284,14 +5284,14 @@
         <v>2</v>
       </c>
       <c r="X40" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>84.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA40" t="n">
@@ -5872,14 +5872,14 @@
         <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA43" t="n">
@@ -6460,14 +6460,14 @@
         <v>2</v>
       </c>
       <c r="X46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y46" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="AA46" t="n">
@@ -6796,14 +6796,14 @@
         <v>9</v>
       </c>
       <c r="X48" t="n">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="Y48" t="n">
-        <v>55</v>
+        <v>26</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>42.3%</t>
         </is>
       </c>
       <c r="AA48" t="n">
